--- a/data/trans_dic/P19C07-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P19C07-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por ortodoncia</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por ortodoncia (tasa de respuesta: 99,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,5; 4,42</t>
+          <t>0,49; 4,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,57; 7,4</t>
+          <t>1,6; 7,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,93; 8,7</t>
+          <t>2,84; 8,76</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,81; 14,26</t>
+          <t>3,22; 15,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,84</t>
+          <t>0,49; 4,79</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,38; 8,52</t>
+          <t>2,43; 8,28</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,91; 11,94</t>
+          <t>5,29; 12,11</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,18; 10,65</t>
+          <t>4,14; 10,55</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,95; 3,61</t>
+          <t>0,91; 3,54</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,66; 6,66</t>
+          <t>2,74; 6,63</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,55; 8,78</t>
+          <t>4,62; 9,1</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,58; 11,13</t>
+          <t>4,49; 10,87</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,5; 5,13</t>
+          <t>1,55; 5,2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,68; 6,7</t>
+          <t>2,76; 6,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,84; 4,13</t>
+          <t>1,08; 4,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,15; 6,12</t>
+          <t>2,06; 5,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,6; 6,53</t>
+          <t>2,56; 6,49</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,2; 4,5</t>
+          <t>1,37; 4,53</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,28; 4,51</t>
+          <t>1,35; 4,66</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,84; 7,82</t>
+          <t>3,88; 7,9</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,56; 5,09</t>
+          <t>2,58; 5,07</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,22; 4,89</t>
+          <t>2,36; 4,84</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,54; 3,58</t>
+          <t>1,45; 3,65</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,29; 5,99</t>
+          <t>3,26; 6,07</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,43; 3,88</t>
+          <t>0,42; 4,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,2; 4,63</t>
+          <t>1,29; 4,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,32; 5,48</t>
+          <t>1,52; 5,5</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,86; 4,83</t>
+          <t>0,83; 4,54</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,68; 4,07</t>
+          <t>0,68; 4,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,12; 6,59</t>
+          <t>2,08; 6,33</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,57; 5,94</t>
+          <t>1,55; 5,94</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,89; 3,41</t>
+          <t>0,84; 3,31</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,93; 3,33</t>
+          <t>0,93; 3,36</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,18; 5,12</t>
+          <t>2,07; 4,76</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,99; 4,83</t>
+          <t>1,93; 4,99</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,01; 3,2</t>
+          <t>1,05; 3,07</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,39; 5,82</t>
+          <t>1,42; 5,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,5; 6,28</t>
+          <t>1,29; 5,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,12; 4,98</t>
+          <t>0,95; 5,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,38; 7,56</t>
+          <t>0,35; 5,94</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,81; 9,56</t>
+          <t>3,84; 9,7</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,53; 7,63</t>
+          <t>2,56; 6,85</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,37; 4,83</t>
+          <t>1,38; 4,66</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,57; 3,06</t>
+          <t>0,54; 3,06</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,13; 6,68</t>
+          <t>3,11; 6,67</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,3; 5,54</t>
+          <t>2,39; 5,69</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,66; 4,34</t>
+          <t>1,48; 4,1</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,68; 3,24</t>
+          <t>0,8; 3,4</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,13; 8,73</t>
+          <t>2,26; 9,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,04; 5,82</t>
+          <t>1,01; 5,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,93; 10,11</t>
+          <t>2,36; 10,96</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,12; 5,77</t>
+          <t>1,1; 6,01</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,25; 7,71</t>
+          <t>1,55; 8,65</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,02; 6,12</t>
+          <t>1,02; 5,94</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,25; 7,34</t>
+          <t>1,23; 7,38</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,45; 6,73</t>
+          <t>1,49; 6,18</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,44; 6,6</t>
+          <t>2,46; 6,81</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,53; 4,78</t>
+          <t>1,53; 5,09</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,38; 7,07</t>
+          <t>2,16; 7,1</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,59; 4,67</t>
+          <t>1,74; 4,74</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,45</t>
+          <t>0,0; 3,5</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,16; 5,35</t>
+          <t>1,15; 5,48</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,4; 4,05</t>
+          <t>0,41; 4,09</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,59; 4,66</t>
+          <t>0,59; 4,75</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,5; 4,42</t>
+          <t>0,5; 4,34</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,39; 7,96</t>
+          <t>2,5; 7,92</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,45; 9,51</t>
+          <t>3,47; 9,67</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,5; 3,05</t>
+          <t>0,51; 2,83</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,5; 3,0</t>
+          <t>0,5; 2,99</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2,24; 5,96</t>
+          <t>2,26; 5,95</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,35; 5,52</t>
+          <t>2,4; 5,7</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,75; 3,35</t>
+          <t>0,79; 3,29</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,19; 5,52</t>
+          <t>2,16; 5,83</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,21; 6,01</t>
+          <t>2,32; 5,89</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,5; 3,17</t>
+          <t>0,49; 2,96</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,19; 5,43</t>
+          <t>2,21; 5,53</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,67; 4,7</t>
+          <t>1,67; 4,68</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,59; 4,32</t>
+          <t>1,68; 4,22</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,12; 4,28</t>
+          <t>1,19; 4,4</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,74; 6,7</t>
+          <t>2,07; 6,66</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,27; 4,49</t>
+          <t>2,25; 4,53</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2,26; 4,46</t>
+          <t>2,23; 4,47</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,14; 2,99</t>
+          <t>1,04; 2,99</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,47; 5,57</t>
+          <t>2,36; 5,41</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,71; 7,65</t>
+          <t>3,88; 8,09</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,91; 4,66</t>
+          <t>1,92; 4,63</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,19; 5,09</t>
+          <t>2,07; 4,98</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,21; 4,67</t>
+          <t>1,12; 4,65</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,34; 5,52</t>
+          <t>2,44; 5,55</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,54; 5,68</t>
+          <t>2,55; 5,63</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,17; 4,98</t>
+          <t>2,15; 5,0</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>3,31; 6,49</t>
+          <t>3,41; 6,47</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3,44; 5,98</t>
+          <t>3,44; 6,01</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2,53; 4,58</t>
+          <t>2,59; 4,69</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2,46; 4,44</t>
+          <t>2,49; 4,52</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,12; 4,88</t>
+          <t>2,29; 4,82</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,7; 4,23</t>
+          <t>2,73; 4,26</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,68; 4,04</t>
+          <t>2,71; 4,06</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,24; 3,64</t>
+          <t>2,16; 3,52</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,39; 4,2</t>
+          <t>2,35; 4,14</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,83; 4,27</t>
+          <t>2,81; 4,22</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,95; 4,36</t>
+          <t>2,94; 4,27</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,93; 4,32</t>
+          <t>2,95; 4,3</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3,13; 4,7</t>
+          <t>3,07; 4,62</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,0; 4,01</t>
+          <t>2,97; 3,95</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3,03; 3,97</t>
+          <t>2,98; 3,96</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2,77; 3,72</t>
+          <t>2,76; 3,82</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2,92; 4,19</t>
+          <t>2,96; 4,15</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por ortodoncia</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por ortodoncia (tasa de respuesta: 99,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>951; 8469</t>
+          <t>943; 8481</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3943; 18549</t>
+          <t>4009; 18161</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7188; 21327</t>
+          <t>6974; 21490</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8579; 43562</t>
+          <t>9841; 46703</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>989; 9740</t>
+          <t>990; 9645</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5941; 21246</t>
+          <t>6057; 20636</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12085; 29414</t>
+          <t>13028; 29840</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>12018; 30626</t>
+          <t>11906; 30330</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3721; 14196</t>
+          <t>3555; 13883</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13282; 33285</t>
+          <t>13705; 33122</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22388; 43163</t>
+          <t>22730; 44735</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>27164; 66026</t>
+          <t>26628; 64491</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6160; 21033</t>
+          <t>6363; 21291</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10891; 27234</t>
+          <t>11206; 27680</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3053; 14995</t>
+          <t>3906; 15096</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10917; 31044</t>
+          <t>10435; 29919</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11455; 28802</t>
+          <t>11305; 28638</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5251; 19693</t>
+          <t>6011; 19816</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5037; 17728</t>
+          <t>5299; 18343</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>19254; 39203</t>
+          <t>19462; 39620</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>21820; 43330</t>
+          <t>21988; 43157</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18765; 41244</t>
+          <t>19942; 40844</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11619; 27076</t>
+          <t>10986; 27606</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>33220; 60442</t>
+          <t>32885; 61199</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1018; 9181</t>
+          <t>1003; 9520</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3525; 13604</t>
+          <t>3775; 14318</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3823; 15910</t>
+          <t>4419; 15988</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2577; 14541</t>
+          <t>2505; 13674</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1952; 11752</t>
+          <t>1963; 11680</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6982; 21667</t>
+          <t>6827; 20807</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4846; 18279</t>
+          <t>4773; 18290</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3000; 11438</t>
+          <t>2821; 11099</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4881; 17520</t>
+          <t>4909; 17661</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>13572; 31890</t>
+          <t>12879; 29617</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11932; 28924</t>
+          <t>11540; 29881</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6414; 20359</t>
+          <t>6652; 19552</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3706; 15563</t>
+          <t>3793; 15985</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4693; 19652</t>
+          <t>4048; 18590</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3685; 16421</t>
+          <t>3129; 16566</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1178; 23457</t>
+          <t>1089; 18428</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11427; 28646</t>
+          <t>11509; 29063</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8676; 26142</t>
+          <t>8771; 23488</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4793; 16864</t>
+          <t>4803; 16270</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2687; 14485</t>
+          <t>2571; 14470</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>17737; 37855</t>
+          <t>17611; 37851</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>15054; 36360</t>
+          <t>15707; 37333</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11294; 29444</t>
+          <t>10043; 27869</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5321; 25406</t>
+          <t>6291; 26620</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3633; 14867</t>
+          <t>3855; 15469</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1989; 11180</t>
+          <t>1945; 11211</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2298; 12049</t>
+          <t>2816; 13063</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1887; 9712</t>
+          <t>1848; 10116</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2168; 13405</t>
+          <t>2692; 15047</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1988; 11913</t>
+          <t>1976; 11556</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1816; 10687</t>
+          <t>1784; 10731</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2942; 13613</t>
+          <t>3005; 12509</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>8398; 22729</t>
+          <t>8450; 23433</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5907; 18499</t>
+          <t>5924; 19662</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6296; 18719</t>
+          <t>5728; 18803</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>5877; 17325</t>
+          <t>6450; 17579</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 6530</t>
+          <t>0; 6622</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2887; 13373</t>
+          <t>2864; 13711</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>926; 9453</t>
+          <t>965; 9555</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1485; 11817</t>
+          <t>1489; 12047</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1022; 9037</t>
+          <t>1018; 8873</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6317; 21089</t>
+          <t>6629; 20962</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8516; 23514</t>
+          <t>8581; 23897</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1230; 7507</t>
+          <t>1245; 6974</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1975; 11804</t>
+          <t>1972; 11767</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>11540; 30693</t>
+          <t>11646; 30625</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>11276; 26533</t>
+          <t>11515; 27403</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3773; 16763</t>
+          <t>3953; 16472</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>10156; 25619</t>
+          <t>10050; 27087</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>12683; 34572</t>
+          <t>13330; 33858</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2192; 14030</t>
+          <t>2156; 13110</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>13151; 32593</t>
+          <t>13239; 33182</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>8989; 25335</t>
+          <t>9007; 25254</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9932; 27054</t>
+          <t>10536; 26436</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5469; 20870</t>
+          <t>5793; 21438</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>14383; 55514</t>
+          <t>17118; 55128</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>22775; 45102</t>
+          <t>22575; 45451</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>27097; 53585</t>
+          <t>26825; 53685</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>10554; 27810</t>
+          <t>9649; 27758</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>35225; 79539</t>
+          <t>33764; 77318</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>19510; 40194</t>
+          <t>20376; 42535</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>12089; 29549</t>
+          <t>12141; 29364</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>14036; 32563</t>
+          <t>13239; 31908</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>10977; 42442</t>
+          <t>10195; 42287</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>13842; 32706</t>
+          <t>14446; 32877</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>17869; 39881</t>
+          <t>17909; 39540</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>14984; 34433</t>
+          <t>14878; 34570</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>23304; 45667</t>
+          <t>24022; 45519</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>38409; 66871</t>
+          <t>38500; 67230</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>33861; 61244</t>
+          <t>34602; 62632</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>32694; 59168</t>
+          <t>33125; 60157</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>34251; 78707</t>
+          <t>36971; 77773</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>66285; 103953</t>
+          <t>66970; 104631</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>78057; 117722</t>
+          <t>78847; 118212</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>59575; 96885</t>
+          <t>57493; 93752</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>80315; 140899</t>
+          <t>78717; 138984</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>77527; 117081</t>
+          <t>77052; 115636</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>92956; 137195</t>
+          <t>92424; 134191</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>84044; 123999</t>
+          <t>84665; 123209</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>112051; 168116</t>
+          <t>109933; 165198</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>156069; 208510</t>
+          <t>154068; 205090</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>183513; 240628</t>
+          <t>180317; 240083</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>153420; 205803</t>
+          <t>152832; 211060</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>202167; 290346</t>
+          <t>205341; 288038</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19C07-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P19C07-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>5,68%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,43</t>
+          <t>0,49; 4,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,6; 7,25</t>
+          <t>1,64; 7,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,84; 8,76</t>
+          <t>2,71; 8,59</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,22; 15,29</t>
+          <t>2,75; 9,74</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,79</t>
+          <t>0,49; 4,58</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,43; 8,28</t>
+          <t>2,22; 8,01</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,29; 12,11</t>
+          <t>4,84; 11,72</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,14; 10,55</t>
+          <t>3,92; 9,46</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,91; 3,54</t>
+          <t>0,98; 3,88</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,74; 6,63</t>
+          <t>2,55; 6,53</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,62; 9,1</t>
+          <t>4,8; 8,93</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,49; 10,87</t>
+          <t>3,83; 8,17</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,55; 5,2</t>
+          <t>1,66; 5,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,76; 6,81</t>
+          <t>2,73; 6,91</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,08; 4,16</t>
+          <t>0,87; 3,89</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,06; 5,9</t>
+          <t>1,95; 5,72</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,56; 6,49</t>
+          <t>2,65; 6,53</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,37; 4,53</t>
+          <t>1,32; 4,5</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,35; 4,66</t>
+          <t>1,28; 4,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,88; 7,9</t>
+          <t>3,84; 7,9</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,58; 5,07</t>
+          <t>2,5; 5,38</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,36; 4,84</t>
+          <t>2,23; 4,92</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,45; 3,65</t>
+          <t>1,49; 3,86</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,26; 6,07</t>
+          <t>3,22; 6,12</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,42; 4,02</t>
+          <t>0,42; 4,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,29; 4,88</t>
+          <t>1,27; 4,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,52; 5,5</t>
+          <t>1,34; 5,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,83; 4,54</t>
+          <t>0,74; 4,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,68; 4,04</t>
+          <t>0,68; 4,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,08; 6,33</t>
+          <t>2,09; 6,52</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,55; 5,94</t>
+          <t>1,59; 5,8</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,84; 3,31</t>
+          <t>0,79; 3,19</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,93; 3,36</t>
+          <t>0,93; 3,17</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,07; 4,76</t>
+          <t>2,1; 4,81</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,93; 4,99</t>
+          <t>2,01; 4,95</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,05; 3,07</t>
+          <t>1,04; 3,14</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,42; 5,98</t>
+          <t>1,37; 5,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,29; 5,94</t>
+          <t>1,33; 6,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,95; 5,02</t>
+          <t>1,15; 5,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 5,94</t>
+          <t>0,31; 6,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,84; 9,7</t>
+          <t>3,73; 9,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,56; 6,85</t>
+          <t>2,43; 7,09</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,38; 4,66</t>
+          <t>1,39; 4,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,54; 3,06</t>
+          <t>0,94; 4,12</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,11; 6,67</t>
+          <t>3,17; 6,74</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,39; 5,69</t>
+          <t>2,36; 5,56</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,48; 4,1</t>
+          <t>1,58; 4,19</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,8; 3,4</t>
+          <t>0,89; 3,94</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,26; 9,08</t>
+          <t>2,56; 9,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,01; 5,84</t>
+          <t>0,99; 5,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,36; 10,96</t>
+          <t>2,36; 10,35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,1; 6,01</t>
+          <t>1,15; 5,9</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,55; 8,65</t>
+          <t>1,21; 8,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,02; 5,94</t>
+          <t>1,03; 6,01</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,23; 7,38</t>
+          <t>1,24; 7,99</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,49; 6,18</t>
+          <t>1,39; 6,32</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,46; 6,81</t>
+          <t>2,51; 7,0</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,53; 5,09</t>
+          <t>1,49; 5,04</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,16; 7,1</t>
+          <t>2,41; 7,36</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,74; 4,74</t>
+          <t>1,58; 4,75</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,5</t>
+          <t>0,0; 3,82</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,15; 5,48</t>
+          <t>1,14; 5,21</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,41; 4,09</t>
+          <t>0,41; 3,98</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,59; 4,75</t>
+          <t>0,69; 4,81</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,5; 4,34</t>
+          <t>0,5; 4,72</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,5; 7,92</t>
+          <t>2,47; 8,36</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,47; 9,67</t>
+          <t>3,48; 9,16</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,83</t>
+          <t>0,53; 2,89</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,99</t>
+          <t>0,53; 3,15</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2,26; 5,95</t>
+          <t>2,28; 6,04</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,4; 5,7</t>
+          <t>2,35; 5,55</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,79; 3,29</t>
+          <t>0,81; 2,94</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>5,07%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,16; 5,83</t>
+          <t>2,28; 5,81</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,32; 5,89</t>
+          <t>2,4; 5,87</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,96</t>
+          <t>0,49; 2,94</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,21; 5,53</t>
+          <t>2,64; 6,75</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,67; 4,68</t>
+          <t>1,58; 4,63</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,68; 4,22</t>
+          <t>1,61; 4,06</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,19; 4,4</t>
+          <t>1,27; 4,27</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,07; 6,66</t>
+          <t>4,2; 7,96</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,25; 4,53</t>
+          <t>2,25; 4,57</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2,23; 4,47</t>
+          <t>2,28; 4,37</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,04; 2,99</t>
+          <t>1,16; 3,08</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,36; 5,41</t>
+          <t>3,87; 6,53</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,88; 8,09</t>
+          <t>3,73; 7,57</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,92; 4,63</t>
+          <t>1,95; 4,77</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,07; 4,98</t>
+          <t>2,12; 4,92</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,12; 4,65</t>
+          <t>2,69; 5,85</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,44; 5,55</t>
+          <t>2,33; 5,61</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,55; 5,63</t>
+          <t>2,63; 5,61</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,15; 5,0</t>
+          <t>2,05; 4,7</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>3,41; 6,47</t>
+          <t>3,27; 6,33</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3,44; 6,01</t>
+          <t>3,35; 5,98</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2,59; 4,69</t>
+          <t>2,56; 4,66</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2,49; 4,52</t>
+          <t>2,37; 4,42</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,29; 4,82</t>
+          <t>3,37; 5,46</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,73; 4,26</t>
+          <t>2,74; 4,21</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,71; 4,06</t>
+          <t>2,72; 4,11</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,16; 3,52</t>
+          <t>2,26; 3,56</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,35; 4,14</t>
+          <t>2,75; 4,34</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,81; 4,22</t>
+          <t>2,85; 4,2</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,94; 4,27</t>
+          <t>2,98; 4,4</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,95; 4,3</t>
+          <t>2,87; 4,24</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3,07; 4,62</t>
+          <t>3,52; 4,88</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2,97; 3,95</t>
+          <t>2,94; 3,99</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2,98; 3,96</t>
+          <t>2,99; 3,95</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2,76; 3,82</t>
+          <t>2,78; 3,78</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2,96; 4,15</t>
+          <t>3,35; 4,39</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21354</t>
+          <t>15845</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>19605</t>
+          <t>18812</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>40959</t>
+          <t>34656</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>943; 8481</t>
+          <t>939; 8527</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4009; 18161</t>
+          <t>4117; 17705</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6974; 21490</t>
+          <t>6650; 21058</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9841; 46703</t>
+          <t>8263; 29302</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>990; 9645</t>
+          <t>988; 9223</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6057; 20636</t>
+          <t>5536; 19975</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13028; 29840</t>
+          <t>11929; 28881</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>11906; 30330</t>
+          <t>12136; 29268</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3555; 13883</t>
+          <t>3831; 15238</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13705; 33122</t>
+          <t>12729; 32633</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22730; 44735</t>
+          <t>23600; 43906</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>26628; 64491</t>
+          <t>23386; 49892</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17747</t>
+          <t>18202</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>27756</t>
+          <t>29151</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>45503</t>
+          <t>47353</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6363; 21291</t>
+          <t>6819; 21365</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11206; 27680</t>
+          <t>11077; 28076</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3906; 15096</t>
+          <t>3151; 14136</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10435; 29919</t>
+          <t>10080; 29632</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11305; 28638</t>
+          <t>11676; 28817</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6011; 19816</t>
+          <t>5775; 19718</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5299; 18343</t>
+          <t>5029; 18450</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>19462; 39620</t>
+          <t>20413; 41981</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>21988; 43157</t>
+          <t>21251; 45809</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>19942; 40844</t>
+          <t>18783; 41507</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10986; 27606</t>
+          <t>11300; 29177</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>32885; 61199</t>
+          <t>33804; 64238</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6342</t>
+          <t>6132</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5884</t>
+          <t>5843</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12226</t>
+          <t>11975</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1003; 9520</t>
+          <t>1003; 10059</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3775; 14318</t>
+          <t>3734; 14318</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4419; 15988</t>
+          <t>3882; 16901</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2505; 13674</t>
+          <t>2218; 13489</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1963; 11680</t>
+          <t>1957; 11801</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6827; 20807</t>
+          <t>6877; 21423</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4773; 18290</t>
+          <t>4890; 17854</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2821; 11099</t>
+          <t>2710; 10901</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4909; 17661</t>
+          <t>4910; 16671</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12879; 29617</t>
+          <t>13100; 29940</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11540; 29881</t>
+          <t>12043; 29620</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6652; 19552</t>
+          <t>6650; 20130</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5389</t>
+          <t>5972</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>6530</t>
+          <t>8499</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>11919</t>
+          <t>14471</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3793; 15985</t>
+          <t>3659; 15596</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4048; 18590</t>
+          <t>4161; 18848</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3129; 16566</t>
+          <t>3781; 17275</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1089; 18428</t>
+          <t>1147; 22491</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11509; 29063</t>
+          <t>11175; 27498</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8771; 23488</t>
+          <t>8335; 24298</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4803; 16270</t>
+          <t>4840; 17244</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2571; 14470</t>
+          <t>3932; 17273</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>17611; 37851</t>
+          <t>17958; 38238</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>15707; 37333</t>
+          <t>15494; 36485</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10043; 27869</t>
+          <t>10702; 28458</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6291; 26620</t>
+          <t>7066; 31166</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4857</t>
+          <t>5157</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5846</t>
+          <t>6494</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>10702</t>
+          <t>11652</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3855; 15469</t>
+          <t>4366; 15317</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1945; 11211</t>
+          <t>1909; 10346</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2816; 13063</t>
+          <t>2810; 12344</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1848; 10116</t>
+          <t>2172; 11165</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2692; 15047</t>
+          <t>2102; 13938</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1976; 11556</t>
+          <t>2000; 11685</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1784; 10731</t>
+          <t>1801; 11626</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3005; 12509</t>
+          <t>3065; 13899</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>8450; 23433</t>
+          <t>8631; 24103</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5924; 19662</t>
+          <t>5779; 19477</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5728; 18803</t>
+          <t>6378; 19495</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>6450; 17579</t>
+          <t>6462; 19445</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4695</t>
+          <t>4522</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>3230</t>
+          <t>3273</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>7926</t>
+          <t>7795</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 6622</t>
+          <t>0; 7237</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2864; 13711</t>
+          <t>2845; 13017</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>965; 9555</t>
+          <t>959; 9297</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1489; 12047</t>
+          <t>1729; 12003</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1018; 8873</t>
+          <t>1018; 9659</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6629; 20962</t>
+          <t>6540; 22151</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8581; 23897</t>
+          <t>8602; 22650</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1245; 6974</t>
+          <t>1324; 7272</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1972; 11767</t>
+          <t>2074; 12404</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>11646; 30625</t>
+          <t>11725; 31093</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>11515; 27403</t>
+          <t>11289; 26668</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3953; 16472</t>
+          <t>4054; 14748</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>21073</t>
+          <t>30552</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>36136</t>
+          <t>42376</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>57208</t>
+          <t>72928</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>10050; 27087</t>
+          <t>10583; 26985</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>13330; 33858</t>
+          <t>13794; 33733</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2156; 13110</t>
+          <t>2176; 12995</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>13239; 33182</t>
+          <t>18452; 47103</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>9007; 25254</t>
+          <t>8523; 24954</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10536; 26436</t>
+          <t>10063; 25442</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5793; 21438</t>
+          <t>6178; 20773</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>17118; 55128</t>
+          <t>31156; 59036</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>22575; 45451</t>
+          <t>22572; 45918</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>26825; 53685</t>
+          <t>27403; 52486</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>9649; 27758</t>
+          <t>10814; 28658</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>33764; 77318</t>
+          <t>55664; 93909</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>26064</t>
+          <t>31432</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>33371</t>
+          <t>37663</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>59436</t>
+          <t>69095</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>20376; 42535</t>
+          <t>19581; 39794</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>12141; 29364</t>
+          <t>12344; 30267</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>13239; 31908</t>
+          <t>13594; 31493</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>10195; 42287</t>
+          <t>20762; 45120</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>14446; 32877</t>
+          <t>13821; 33225</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>17909; 39540</t>
+          <t>18463; 39422</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>14878; 34570</t>
+          <t>14152; 32518</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>24022; 45519</t>
+          <t>26496; 51321</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>38500; 67230</t>
+          <t>37402; 66900</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>34602; 62632</t>
+          <t>34204; 62210</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>33125; 60157</t>
+          <t>31607; 58859</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>36971; 77773</t>
+          <t>53263; 86381</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>107520</t>
+          <t>117815</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>138358</t>
+          <t>152111</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>245878</t>
+          <t>269926</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>66970; 104631</t>
+          <t>67347; 103332</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>78847; 118212</t>
+          <t>79376; 119741</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>57493; 93752</t>
+          <t>60136; 94876</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>78717; 138984</t>
+          <t>93329; 147596</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>77052; 115636</t>
+          <t>78134; 115038</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>92424; 134191</t>
+          <t>93902; 138327</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>84665; 123209</t>
+          <t>82376; 121465</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>109933; 165198</t>
+          <t>127565; 176936</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>154068; 205090</t>
+          <t>152983; 207455</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>180317; 240083</t>
+          <t>181344; 239580</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>152832; 211060</t>
+          <t>153503; 208873</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>205341; 288038</t>
+          <t>235502; 308107</t>
         </is>
       </c>
     </row>
